--- a/output/step1/tables/表2_缺失率与样本覆盖.xlsx
+++ b/output/step1/tables/表2_缺失率与样本覆盖.xlsx
@@ -555,7 +555,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ret_lag_20</t>
+          <t>USD_20</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,10 +565,10 @@
         <v>0.00386324125941665</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>38749</v>
+        <v>38720</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46003</v>
+        <v>45975</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
@@ -577,29 +577,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BBW_20</t>
+          <t>ret_lag_20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003670079196445818</v>
+        <v>0.00386324125941665</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>38748</v>
+        <v>38749</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MA_gap_20</t>
+          <t>BBW_20</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -621,45 +621,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ret_lag_10</t>
+          <t>MA_gap_20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001931620629708325</v>
+        <v>0.003670079196445818</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>38735</v>
+        <v>38748</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UK_3M</t>
+          <t>ret_lag_10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001352134440795828</v>
+        <v>0.001931620629708325</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>38729</v>
+        <v>38735</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -687,45 +687,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ret_lag_5</t>
+          <t>UK_3M</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0009658103148541626</v>
+        <v>0.001352134440795828</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>38727</v>
+        <v>38729</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BBW_5</t>
+          <t>ret_lag_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0007726482518833301</v>
+        <v>0.0009658103148541626</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>38726</v>
+        <v>38727</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -753,29 +753,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ret_lag_2</t>
+          <t>BBW_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000386324125941665</v>
+        <v>0.0007726482518833301</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>38722</v>
+        <v>38726</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CN_Mkt_Index</t>
+          <t>JP_Mkt_Index</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -797,7 +797,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JP_Mkt_Index</t>
+          <t>ret_lag_2</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -819,23 +819,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GER_Mkt_Index</t>
+          <t>CN_Mkt_Index</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001931620629708325</v>
+        <v>0.000386324125941665</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>38721</v>
+        <v>38722</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US_Mkt_Index</t>
+          <t>GER_Mkt_Index</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -951,7 +951,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>USD_1</t>
+          <t>US_Mkt_Index</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -961,10 +961,10 @@
         <v>0.0001931620629708325</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>38720</v>
+        <v>38721</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
